--- a/backups/history/backup-2026-05-22.xlsx
+++ b/backups/history/backup-2026-05-22.xlsx
@@ -20867,7 +20867,7 @@
         <v>BA1583, BA4598</v>
       </c>
       <c r="G247" t="str">
-        <v>Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21:35:09 BST | Inferred from GPS brackets: evening=New York 2026-04-17 21:48:33 BST, morning= 2026-04-18 21…[TRUNCATED]</v>
+        <v/>
       </c>
       <c r="H247" t="str">
         <v>40.6486852</v>
@@ -20927,7 +20927,7 @@
         <v>Yes</v>
       </c>
       <c r="AA247" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="248">
@@ -21033,7 +21033,7 @@
         <v/>
       </c>
       <c r="G249" t="str">
-        <v>Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST | Inferred from GPS brackets: evening= 2026-04-19 21:07:32 BST, morning= 2026-04-20 12:34:37 BST</v>
+        <v/>
       </c>
       <c r="H249" t="str">
         <v>30.2916689</v>
@@ -21093,7 +21093,7 @@
         <v/>
       </c>
       <c r="AA249" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="250">
